--- a/output/prd_hitl.xlsx
+++ b/output/prd_hitl.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,82 +417,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Item No.</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Requestor Function</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>SubCategory</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>SKUs Applicable</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Requirement (What)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Justification (Why)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>New Threshold (Acceptable to Ship)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Target (Design Goal)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Ambiguity Score</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Clarification Questions</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Response</t>
         </is>
@@ -1991,9 +1979,9 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>What specific metric or performance indicator defines 'optimal' in this context?
-What is the minimum acceptable threshold for this metric?
-Which system or actor is responsible for achieving this requirement?</t>
+          <t>What specific metric defines 'efficient' in this context (e.g., latency in ms, throughput in transactions per second)?
+Which system or actor is responsible for achieving this efficiency?
+Under what operational conditions should the efficiency be measured?</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2069,8 +2057,9 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>What unit of measurement should be applied to the threshold value?
-Which system or actor is responsible for meeting this requirement?</t>
+          <t>What is the specific metric or threshold for reliability (e.g., uptime percentage, mean time between failures)?
+What is the expected unit or range for the 'Goal (Design Target)'?
+Who is responsible for ensuring this reliability?</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2218,9 +2207,9 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>What specific conditions determine when this feature is needed?
-What is the measurable threshold or success criteria for this requirement?
-Which actor or system is responsible for implementing this feature?</t>
+          <t>What does 'adequate' mean in measurable terms (e.g., specific performance or quality criteria)?
+When will the 'Threshold (Accept)' value be finalized?
+Which actor or system is responsible for meeting this requirement?</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2296,8 +2285,8 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>What specific criteria define 'appropriate' in this context?
-Can the threshold be further clarified with exact values or ranges?</t>
+          <t>What specific unit should be associated with the 'Threshold (Accept)' value?
+Under what specific conditions is this requirement considered 'required'?</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -3372,7 +3361,7 @@
         <is>
           <t>What is the maximum acceptable response time in milliseconds?
 Which component — frontend, backend, or network — owns this response time requirement?
-Under what load conditions (concurrent users, requests/second) must this be met?</t>
+Under what load conditions (e.g., concurrent users, requests per second) must this requirement be met?</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -3443,10 +3432,16 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr"/>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>What unit should be applied to the Threshold (Accept) value?
+Who or what system is responsible for achieving this requirement?
+What is the ideal design target value in measurable terms?</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -3513,15 +3508,12 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Which specific languages must be supported at minimum?
-What is the ideal set of languages to support?
-Does 'support' mean full UI translation, content translation, or both?
-Are there any compliance or localization standards to follow?</t>
-        </is>
-      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -3588,13 +3580,16 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Under what conditions must the system log errors?
-What types of errors must be logged?
-What information should be included in each error log?
-What is the minimum acceptable logging frequency or retention policy?</t>
+          <t>What specific criteria define 'appropriate' in this context?
+What is the minimum acceptable threshold (e.g., numeric or categorical value)?
+Who or what system is responsible for fulfilling this requirement?</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -3663,13 +3658,16 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>What usability standards or metrics define 'user-friendly' (e.g., SUS score, error rate, task completion time)?
-Are there specific user personas or accessibility requirements to consider?
-What is the minimum acceptable usability score or benchmark?
-How will user-friendliness be tested and validated?</t>
+          <t>What are the exact success criteria for this requirement?
+Who is responsible for implementing and validating this requirement?
+Are there any boundary conditions or edge cases that should be explicitly stated?</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
@@ -6161,9 +6159,9 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>What specific metric defines 'efficient' (e.g., response time, resource usage, etc.)?
-What is the acceptable range or threshold for this metric?
-Which system or actor is responsible for ensuring this efficiency?</t>
+          <t>What is the maximum acceptable response time in milliseconds?
+Which component — frontend, backend, or network — owns this response time requirement?
+Under what load conditions (concurrent users, requests/second) must this be met?</t>
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
@@ -6234,16 +6232,10 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>What units should be applied to the threshold (e.g., seconds, milliseconds, percentage)?
-What specific criteria define 'acceptable performance'?
-Which system or component is responsible for meeting this requirement?</t>
-        </is>
-      </c>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
@@ -6306,12 +6298,14 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Which specific languages must the application support at minimum?
+What is the target number or list of languages for full support?
+What does 'support' entail (UI translation, content localization, input validation, etc.)?</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
@@ -6374,16 +6368,12 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
-          <t>What specific conditions determine when this requirement is 'required'?
-What is the measurable threshold for this requirement once defined?
-Which system or actor is responsible for fulfilling this requirement?</t>
+          <t>Under what specific conditions should notifications be sent to users?
+Who or what determines when a notification is necessary?
+What is the acceptable delivery time for notifications (e.g., within X seconds of event)?</t>
         </is>
       </c>
       <c r="P85" t="inlineStr"/>
@@ -6448,16 +6438,12 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
-          <t>What specific metric defines 'optimal' in this context (e.g., speed, efficiency, etc.)?
-What is the numerical target or range for the 'Goal (Design Target)'?
-Which system or actor is responsible for achieving this goal?</t>
+          <t>What is the minimum acceptable system uptime percentage (e.g., 99.9%)?
+What is the target system uptime percentage?
+Over what time period is uptime measured (monthly, yearly)?</t>
         </is>
       </c>
       <c r="P86" t="inlineStr"/>
@@ -7538,9 +7524,9 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>What is the specific efficiency metric being measured (e.g., CPU usage, throughput, energy consumption)?
-What is the acceptable range or numeric value for efficiency?
-Which system or component is responsible for achieving this efficiency?</t>
+          <t>What is the maximum acceptable response time in milliseconds?
+Which component — frontend, backend, or network — owns this response time requirement?
+Under what load conditions (concurrent users, requests/second) must this be met?</t>
         </is>
       </c>
       <c r="P102" t="inlineStr"/>
@@ -7611,16 +7597,10 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>What units should be applied to the threshold value (e.g., seconds, percentage, etc.)?
-Who or what component is responsible for ensuring sufficiency in this context?
-What constitutes 'sufficient' in measurable terms?</t>
-        </is>
-      </c>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
     </row>
     <row r="104">
@@ -7689,12 +7669,14 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>What specific authentication mechanisms or protocols are required (e.g., OAuth2, multi-factor authentication)?
+What are the measurable criteria for 'robust' authentication (e.g., resistance to brute-force attacks, minimum password complexity)?
+Who is responsible for implementing and maintaining user authentication?</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
@@ -7761,16 +7743,12 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
-          <t>What are the specific conditions under which this requirement is 'required'?
-What is the numeric or measurable threshold for this requirement?
-Who or what system is responsible for fulfilling this requirement?</t>
+          <t>Which specific languages must the application support at minimum?
+What is the ideal set of languages to be supported?
+What does 'support' entail (e.g., full UI translation, help documentation, error messages)?</t>
         </is>
       </c>
       <c r="P105" t="inlineStr"/>
@@ -7839,16 +7817,12 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
-          <t>What units should be applied to the threshold value?
-What is the ideal design target for this requirement?
-Who or what system is responsible for achieving this requirement?</t>
+          <t>What is the minimum acceptable system uptime percentage (e.g., 99.9%)?
+What is the ideal system uptime target?
+Over what time period is uptime measured (e.g., monthly, annually)?</t>
         </is>
       </c>
       <c r="P106" t="inlineStr"/>

--- a/output/prd_hitl.xlsx
+++ b/output/prd_hitl.xlsx
@@ -569,1421 +569,1427 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>What specific metric defines 'efficient' in this context (e.g., CPU usage, memory consumption)?
+What is the acceptable range or threshold for this efficiency metric?
+Who or what system component is responsible for ensuring efficiency?</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Maximum allowable printer tilt angle is 20 degrees while maintaining specified print quality and system operation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mechanical Integrity</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Marconi Base LP2, Marconi Base LP1, Marconi Hi, PDL SKUs, Manhattan Base &amp; Hi, Malbec Hi, Agave</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Clear paper jam and check if encoder strip will drop when printer is tilted left and right to 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20220704(Sau Pin): Marconi Base LP2 test no issue reported. 20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going interesting to find out the test result. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with standard UBT requirement.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Meet customer requirement</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>What specific metric defines 'sufficient capacity' (e.g., GB, number of users)?
+What is the unit of measurement for the provided threshold?
+Which system component is responsible for meeting this capacity requirement?</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>The system shall provide secure paper-clearance procedures that prevent unauthorized access, damage, or safety hazards during maintenance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mechanical Robustness</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>LP1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Improve robustness of gate handoff to prevent breakage or deformation during paper jam events. Target for LP1.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20220315 (Sau Pin): Design Changed aligned and released for LP1 testing 20210607 (Jeffrey/TH): Under investigation, budget catered make proto to verify new design. Close up the slot, similar to sayan. Stronger piece. Target for LP1.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Better than current Manhattan units.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Minimum required improvement shall be defined as a measurable increase over the current baseline performance (e.g., ≥10% improvement unless otherwise specified).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sensor Feedback</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CD1, CD2, Cleanout latch process</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Improve feedback for cleanout/duplexer missing by adding a dedicated sensor and improving firmware feedback. Sensor should not be tied to other sensors.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20220315(Sau Pin): Design improvement to Cleanout to prevent/limit twist implemented. Need final alignment with requestor 20210607 (Jeffrey/TH): Improved solution planned &amp; to be verified in CD2; CD1 design as threshold/back-up, budget catered Is it possible to add conduct circuit to detect latch? plan prototype to improve cleanout latch process to reduce the issue. 20210617AQ: it would be very expensive to add cleanout sensor (estimate $0.8~1)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Better than current Manhattan units.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>What specific attributes or metrics define 'robust' in this context (e.g., uptime percentage, error tolerance)?
+What is the acceptable threshold or range for these robustness metrics?
+Which system or component is responsible for ensuring robustness?</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Usability shall be measured using agreed metrics such as task completion rate, error rate, and user satisfaction score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Print System Reliability</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Manhattan, Yeti, Marconi</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Eliminate Print System Problem by identifying root cause and implementing fix to prevent field failures.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20230307(SP): No reported incident. Will change status to "Green". 20221209(SP): To monitor until MC checkpoint 202210315(Sau Pin):This is on-going investigation in Manhattan. Will apply fix, if any and qualified 20210607 (Jeffrey): To follow up with Pock Chueng Current issue on Manhattan and Yeti. the current team need to continue investigate the unknown root cause. If identified then we look for opportunity to implement on Marconi. Pauline is working on it for Manhattan and Yeti. 20220118 (AQ, Boon Hock, Tracy, ZJ) the PSP taskforce is still working on this issue. We continue checking field return units. So far most of the returned units are recoverable therefore difficult to find out the root cause of the failure. May request more EE resource on this taskforce (to identify the EE support).</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Better than or equal to current Manhattan</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>What specific conditions determine when this requirement is 'needed'?
+What system or actor is responsible for executing this requirement when needed?
+Is there a default behavior if the condition is not met?</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Minimum requirement is complete elimination of the identified issue under normal operating conditions, with no recurrence during validation testing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Paper Handling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Manhattan, Marconi</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Implement paper de-skew function so printer can correct skewed paper during pick and guide media to a straight path.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>202200316(SP): This is already in current Manhattan product.No change to Marconi program When Paper is skewed during pick, printer can move the media in and out and guide the media to a straight path into the paper path (Normal and Best)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>as per current Manhattan, Turn roller deskew and Feed roller deskew</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Media Handling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Manhattan, Marconi Base LP2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Improve pick of special media such as card or thick media by adding ribs on tray to increase stiffness and help media pick.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20220704(SP): Marconi Base LP2 DET completed and meeting intervention. Change to "Green" as Threshold is same as Manhattan 20220315(SP): Need to clarify with Requestor on the issue. Change to "Yellow" as Threshold is same as Manhattan investigate card media pick improvements. Plan to add ribs on tray to increase the stiffness, which will help media pick.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>as per current manhattan</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Cosmetic Quality</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Manhattan, SF, 3M</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>No cosmetic aerosol should be visible on new White case parts for 3M; requirement is stricter than Manhattan.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20230307(SP):  SF 10K review  and Hi 15K review with TEM. Aligned to keep to current condition. Similar to Manhattan 20221129 (ZJ): AIO expectation is the same as Manhattan =&gt; Status to be Green. SF status check WIP =&gt; Status Yellow 20220315(SP): Test on-going. Will review after LP1 test are completed undergoing aerosol test for batch priming currently.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Same as Manhattan</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Duty Cycle</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Marconi Hi, Manhattan</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Printer must achieve minimum 30,000 pages duty cycle, goal 50,000 pages for Marconi Hi.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20221129(SP/ZJ): XXL supplies confirmed. No impact to Duty Cycle. change status to Green 20220926(Sau Pin): With XL supplies removed, page yield will reduce and will impact duty cycle numbers 20220316(SP): No Change from Manhattan 20210702 (Mandy, Jeffrey): Review when LP1 result available (w/o HW change, test more than predecessor) Waste ink is the bottleneck. We cannot do more than 30k in a month, ink will flow out. 20211011 (Jeffrey): Based on aligned mech lift with Waka Marconi Hi PDL will be about 30K, therefore accept Threshold</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Min 30,000 pages, goal 50,000</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Duty Cycle</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Marconi Base</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>The printer must withstand tilting left and right at 20 degrees while printing for a minimum of 25,000 pages, with a goal of 30,000 pages, without functional failure.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi. Threshold should be manhattan base 20k, waste ink for manhattan base is 20k in a month. Based on aligned mech life with Waka, will target 25K Duty cycle, so accept Threshold.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Min 25,000 pages</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Goal 30,000 pages</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Monthly Recommended Print volume</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Marconi Base, Marconi Hi</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>The printer should support a monthly recommended print volume of 1,500 pages for Marconi Base and 2,000 pages for Marconi Hi while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi. Need Clarification.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1,500 for Marconi Base, 2,000 for Marconi Hi</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1,500 for Marconi Base, 2,000 for Marconi Hi</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Marconi Hi</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>The printer must achieve a mechanical life of at least 60,000 pages (target 100,000 pages) for Marconi Hi SKU while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>No Hardware reliability issue to meet 60K for Hi/PDL-hi. Base LP2 Life test completed. PDL-Base on-going. Hi/PDl-Hi LP2 test ongoing. LP1 test still on-going. DDO test in progress, but only 2 units. aerosol test in progress. full qual will be in LP1.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>60,000 pages</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>100,000 pages</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Marconi Base</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>The printer must achieve a mechanical life of at least 45,000 pages (target 80,000 pages) for Marconi Base SKU while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Marconi Base LP2 DET completed and no hardware failure reported. LP1 test completed with defect investigation on-going. aerosol test in progress.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>45,000 pages</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>80,000 pages</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>19</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Borderless Printing</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>The printer must support borderless photo printing and enable 100% copy reproduction while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Same as Manhattan. Manhattan/Malbec support 4x6 borderless photo copy. As the printout need to be borderless, the reproduction photo is actually magnified a little bit. We want to know if the request is to follow Malbec, or is there anything new.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Support borderless photo printing</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Enable 100% copy reproduction</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Input tray capacity</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Input Tray Capacity</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Marconi Base, Marconi Hi</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>The printer must maintain Manhattan input tray capacity: Marconi Base 250 sheets, Marconi Hi 250 + 250 sheets, while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>No Change from Manhattan program, same as Manhattan.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Marconi Base 250 sheets, Marconi Hi 250 + 250 sheets</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Maintain Manhattan input tray capacity</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Output paper tray</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Output Paper Tray Capacity</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Marconi Base, Marconi Hi</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>The printer should support an output paper tray capacity of 100 sheets for both Marconi Base and Marconi Hi SKUs while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Output Management Test with LP2 Life Test units show same performance as Manhattan. Need to review Marconi Base LP1 testing result. Need to conduct RnD validation test for Base SKU to support up to 80 sheets. Manhattan Base can accommodate around 80 sheets without ME modification. To align with marketing to test up to 80 on Marconi Base.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>100 sheets for both Marconi Base and Marconi Hi</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>100 sheets output paper tray capacity</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>23</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Media Size</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Media Size Supported</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>The printer must support the following media sizes: Letter, Legal, Government Legal, Executive, Statement, 3x5 in, 4x6 in, 5x7 in, 13x18 cm, 8x10 in, 10x15 cm, L, Photo 2L, Envelope (#10, Monarch, 5.5 bar), Card (3x5 in, 4x6 in, 5x8 in), Hagaki, 5x5, 4x5, and 4x12 inch HP branded photo media while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Mech is able to support these media size. New media size added need to evaluated performance and accept as it is. Accept.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Support listed media sizes</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Support listed media sizes</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>24</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Mandy Hagedorn</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Media Sizes</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Expanded Photo Media Handling</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Marconi Base</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>The printer must support expanded photo media handling for 5x5 and 4x12 inch sizes for Marconi Base SKU while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Marconi Base LP2 DET completed and able to support expanded photo media handling for 5x5 and 4x12. LP1 test with media still on-going. Follow Novelli solution.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Support expanded photo media handling for 5x5 and 4x12 inch sizes</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Support expanded photo media handling for 5x5 and 4x12 inch sizes</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>25</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Mandy Hagedorn</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Simplex and Duplex Printing</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Assess functional failure when printer is tilted left and right at 20 degrees during printing. Follow Novelli solution for simplex and duplex print on brochure and photo media. Wider bottom margin (0.50 inch) and less ink on first side, with UI changes for media type selection.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Follow Novelli solution and align with TME and Marketing to drop this. Novelli investigated duplex on 4x6 Photo Matte media and proposed UI changes for media type selection to avoid mech limitation issues.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Follow Novelli solution</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>26</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ben / Ricker</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Remove LDV, change to 4HC. Print quality should be same as Malbec. Evaluate functional failure when printer is tilted left and right at 20 degrees during printing. Accept threshold for drop.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>No change from Manhattan. Marconi has bigger swath height and printmode is more sensitive to linefeed error. LDV cannot be removed but parameter setting may be possible per vendor.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Same as Manhattan</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>28</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Celine Taccori</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Quiet Mode</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>GxD</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Quiet mode activation during printing must be instantaneous and result in a noticeable reduction in noise, confirmed by user perception.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Same as Manhattan/Malbec. Majority delivered in FW BR3 except trigger in middle of printing planned post BR3.1. User must hear difference when quiet mode is activated.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Quiet mode should be instantaneous and hearable</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
           <t>What is the maximum acceptable response time in milliseconds?
 Which component — frontend, backend, or network — owns this response time requirement?
 Under what load conditions (concurrent users, requests/second) must this be met?</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Maximum allowable printer tilt angle is 20 degrees while maintaining specified print quality and system operation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Chong, Shin</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Mechanical Integrity</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Marconi Base LP2, Marconi Base LP1, Marconi Hi, PDL SKUs, Manhattan Base &amp; Hi, Malbec Hi, Agave</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Clear paper jam and check if encoder strip will drop when printer is tilted left and right to 20 degrees during printing.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20220704(Sau Pin): Marconi Base LP2 test no issue reported. 20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going interesting to find out the test result. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with standard UBT requirement.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>The system shall provide secure paper-clearance procedures that prevent unauthorized access, damage, or safety hazards during maintenance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Tracy Foo</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Mechanical Robustness</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>LP1</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Improve robustness of gate handoff to prevent breakage or deformation during paper jam events. Target for LP1.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20220315 (Sau Pin): Design Changed aligned and released for LP1 testing 20210607 (Jeffrey/TH): Under investigation, budget catered make proto to verify new design. Close up the slot, similar to sayan. Stronger piece. Target for LP1.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Better than current Manhattan units.</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>What is the minimum number of concurrent users the application must support (threshold)?
-What is the ideal (design target) number of concurrent users?
-How is 'concurrent user' defined (active sessions, logged-in users, requests per second)?
-How will the system's ability to handle concurrent users be tested?
-Are there specific performance metrics (e.g., response time, error rate) under load?</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Minimum required improvement shall be defined as a measurable increase over the current baseline performance (e.g., ≥10% improvement unless otherwise specified).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Tracy Foo</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Sensor Feedback</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>CD1, CD2, Cleanout latch process</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Improve feedback for cleanout/duplexer missing by adding a dedicated sensor and improving firmware feedback. Sensor should not be tied to other sensors.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20220315(Sau Pin): Design improvement to Cleanout to prevent/limit twist implemented. Need final alignment with requestor 20210607 (Jeffrey/TH): Improved solution planned &amp; to be verified in CD2; CD1 design as threshold/back-up, budget catered Is it possible to add conduct circuit to detect latch? plan prototype to improve cleanout latch process to reduce the issue. 20210617AQ: it would be very expensive to add cleanout sensor (estimate $0.8~1)</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Better than current Manhattan units.</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>What usability metrics or standards should be used to define 'intuitive' and 'easy to use' (e.g., SUS score, task completion rate)?
-Is there a target user group or persona for usability testing?
-What is the minimum acceptable usability score or user satisfaction rating?
-How will usability be measured and validated?
-Are there specific accessibility or design guidelines to follow?</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Usability shall be measured using agreed metrics such as task completion rate, error rate, and user satisfaction score.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Tracy Foo</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Print System Reliability</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Manhattan, Yeti, Marconi</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Eliminate Print System Problem by identifying root cause and implementing fix to prevent field failures.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20230307(SP): No reported incident. Will change status to "Green". 20221209(SP): To monitor until MC checkpoint 202210315(Sau Pin):This is on-going investigation in Manhattan. Will apply fix, if any and qualified 20210607 (Jeffrey): To follow up with Pock Chueng Current issue on Manhattan and Yeti. the current team need to continue investigate the unknown root cause. If identified then we look for opportunity to implement on Marconi. Pauline is working on it for Manhattan and Yeti. 20220118 (AQ, Boon Hock, Tracy, ZJ) the PSP taskforce is still working on this issue. We continue checking field return units. So far most of the returned units are recoverable therefore difficult to find out the root cause of the failure. May request more EE resource on this taskforce (to identify the EE support).</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Better than or equal to current Manhattan</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>What is the minimum acceptable system uptime percentage (e.g., 99.9%)?
-What is the ideal (design target) uptime?
-Over what period is uptime measured (monthly, yearly)?
-Does uptime include scheduled maintenance windows?
-How will uptime be monitored and reported?</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Minimum requirement is complete elimination of the identified issue under normal operating conditions, with no recurrence during validation testing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Tracy Foo</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Paper Handling</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Manhattan, Marconi</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Implement paper de-skew function so printer can correct skewed paper during pick and guide media to a straight path.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>202200316(SP): This is already in current Manhattan product.No change to Marconi program When Paper is skewed during pick, printer can move the media in and out and guide the media to a straight path into the paper path (Normal and Best)</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>as per current Manhattan, Turn roller deskew and Feed roller deskew</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>WANT</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Tracy Foo</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Media Handling</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Manhattan, Marconi Base LP2</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Improve pick of special media such as card or thick media by adding ribs on tray to increase stiffness and help media pick.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20220704(SP): Marconi Base LP2 DET completed and meeting intervention. Change to "Green" as Threshold is same as Manhattan 20220315(SP): Need to clarify with Requestor on the issue. Change to "Yellow" as Threshold is same as Manhattan investigate card media pick improvements. Plan to add ribs on tray to increase the stiffness, which will help media pick.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>as per current manhattan</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>13</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Tracy Foo</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Cosmetic Quality</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Manhattan, SF, 3M</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>No cosmetic aerosol should be visible on new White case parts for 3M; requirement is stricter than Manhattan.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20230307(SP):  SF 10K review  and Hi 15K review with TEM. Aligned to keep to current condition. Similar to Manhattan 20221129 (ZJ): AIO expectation is the same as Manhattan =&gt; Status to be Green. SF status check WIP =&gt; Status Yellow 20220315(SP): Test on-going. Will review after LP1 test are completed undergoing aerosol test for batch priming currently.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Same as Manhattan</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>WANT</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>14</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Itsushi Wakabayashi</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Duty Cycle</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Marconi Hi, Manhattan</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Printer must achieve minimum 30,000 pages duty cycle, goal 50,000 pages for Marconi Hi.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20221129(SP/ZJ): XXL supplies confirmed. No impact to Duty Cycle. change status to Green 20220926(Sau Pin): With XL supplies removed, page yield will reduce and will impact duty cycle numbers 20220316(SP): No Change from Manhattan 20210702 (Mandy, Jeffrey): Review when LP1 result available (w/o HW change, test more than predecessor) Waste ink is the bottleneck. We cannot do more than 30k in a month, ink will flow out. 20211011 (Jeffrey): Based on aligned mech lift with Waka Marconi Hi PDL will be about 30K, therefore accept Threshold</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Min 30,000 pages, goal 50,000</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>15</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Itsushi Wakabayashi</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Duty Cycle</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Marconi Base</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>The printer must withstand tilting left and right at 20 degrees while printing for a minimum of 25,000 pages, with a goal of 30,000 pages, without functional failure.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi. Threshold should be manhattan base 20k, waste ink for manhattan base is 20k in a month. Based on aligned mech life with Waka, will target 25K Duty cycle, so accept Threshold.</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Min 25,000 pages</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Goal 30,000 pages</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>16</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Itsushi Wakabayashi</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Monthly Recommended Print volume</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Marconi Base, Marconi Hi</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>The printer should support a monthly recommended print volume of 1,500 pages for Marconi Base and 2,000 pages for Marconi Hi while tilted left and right at 20 degrees during printing.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi. Need Clarification.</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1,500 for Marconi Base, 2,000 for Marconi Hi</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1,500 for Marconi Base, 2,000 for Marconi Hi</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>17</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Itsushi Wakabayashi</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Mech Life</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Marconi Hi</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>The printer must achieve a mechanical life of at least 60,000 pages (target 100,000 pages) for Marconi Hi SKU while tilted left and right at 20 degrees during printing.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>No Hardware reliability issue to meet 60K for Hi/PDL-hi. Base LP2 Life test completed. PDL-Base on-going. Hi/PDl-Hi LP2 test ongoing. LP1 test still on-going. DDO test in progress, but only 2 units. aerosol test in progress. full qual will be in LP1.</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>60,000 pages</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>100,000 pages</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>18</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Itsushi Wakabayashi</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Mech Life</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Marconi Base</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>The printer must achieve a mechanical life of at least 45,000 pages (target 80,000 pages) for Marconi Base SKU while tilted left and right at 20 degrees during printing.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Marconi Base LP2 DET completed and no hardware failure reported. LP1 test completed with defect investigation on-going. aerosol test in progress.</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>45,000 pages</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>80,000 pages</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>19</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Itsushi Wakabayashi</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Borderless Printing</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>The printer must support borderless photo printing and enable 100% copy reproduction while tilted left and right at 20 degrees during printing.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Same as Manhattan. Manhattan/Malbec support 4x6 borderless photo copy. As the printout need to be borderless, the reproduction photo is actually magnified a little bit. We want to know if the request is to follow Malbec, or is there anything new.</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Support borderless photo printing</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Enable 100% copy reproduction</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>21</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Itsushi Wakabayashi</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Input tray capacity</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Input Tray Capacity</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Marconi Base, Marconi Hi</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>The printer must maintain Manhattan input tray capacity: Marconi Base 250 sheets, Marconi Hi 250 + 250 sheets, while tilted left and right at 20 degrees during printing.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>No Change from Manhattan program, same as Manhattan.</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Marconi Base 250 sheets, Marconi Hi 250 + 250 sheets</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Maintain Manhattan input tray capacity</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>22</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Itsushi Wakabayashi</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Output paper tray</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Output Paper Tray Capacity</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Marconi Base, Marconi Hi</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>The printer should support an output paper tray capacity of 100 sheets for both Marconi Base and Marconi Hi SKUs while tilted left and right at 20 degrees during printing.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Output Management Test with LP2 Life Test units show same performance as Manhattan. Need to review Marconi Base LP1 testing result. Need to conduct RnD validation test for Base SKU to support up to 80 sheets. Manhattan Base can accommodate around 80 sheets without ME modification. To align with marketing to test up to 80 on Marconi Base.</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>100 sheets for both Marconi Base and Marconi Hi</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>100 sheets output paper tray capacity</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>23</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Itsushi Wakabayashi</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Media Size</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Media Size Supported</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>The printer must support the following media sizes: Letter, Legal, Government Legal, Executive, Statement, 3x5 in, 4x6 in, 5x7 in, 13x18 cm, 8x10 in, 10x15 cm, L, Photo 2L, Envelope (#10, Monarch, 5.5 bar), Card (3x5 in, 4x6 in, 5x8 in), Hagaki, 5x5, 4x5, and 4x12 inch HP branded photo media while tilted left and right at 20 degrees during printing.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Mech is able to support these media size. New media size added need to evaluated performance and accept as it is. Accept.</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Support listed media sizes</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Support listed media sizes</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>24</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Mandy Hagedorn</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Media Sizes</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Expanded Photo Media Handling</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Marconi Base</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>The printer must support expanded photo media handling for 5x5 and 4x12 inch sizes for Marconi Base SKU while tilted left and right at 20 degrees during printing.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Marconi Base LP2 DET completed and able to support expanded photo media handling for 5x5 and 4x12. LP1 test with media still on-going. Follow Novelli solution.</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Support expanded photo media handling for 5x5 and 4x12 inch sizes</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Support expanded photo media handling for 5x5 and 4x12 inch sizes</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>25</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Mandy Hagedorn</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Simplex and Duplex Printing</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Assess functional failure when printer is tilted left and right at 20 degrees during printing. Follow Novelli solution for simplex and duplex print on brochure and photo media. Wider bottom margin (0.50 inch) and less ink on first side, with UI changes for media type selection.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Follow Novelli solution and align with TME and Marketing to drop this. Novelli investigated duplex on 4x6 Photo Matte media and proposed UI changes for media type selection to avoid mech limitation issues.</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Follow Novelli solution</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>26</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Ben / Ricker</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>OPS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Print Quality</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Remove LDV, change to 4HC. Print quality should be same as Malbec. Evaluate functional failure when printer is tilted left and right at 20 degrees during printing. Accept threshold for drop.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>No change from Manhattan. Marconi has bigger swath height and printmode is more sensitive to linefeed error. LDV cannot be removed but parameter setting may be possible per vendor.</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Same as Manhattan</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>28</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Celine Taccori</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Quiet Mode</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>GxD</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Quiet mode activation during printing must be instantaneous and result in a noticeable reduction in noise, confirmed by user perception.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Same as Manhattan/Malbec. Majority delivered in FW BR3 except trigger in middle of printing planned post BR3.1. User must hear difference when quiet mode is activated.</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Quiet mode should be instantaneous and hearable</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>What specific metric defines 'efficient' in this context (e.g., latency in ms, throughput in transactions per second)?
-Which system or actor is responsible for achieving this efficiency?
-Under what operational conditions should the efficiency be measured?</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -2052,16 +2058,10 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>What is the specific metric or threshold for reliability (e.g., uptime percentage, mean time between failures)?
-What is the expected unit or range for the 'Goal (Design Target)'?
-Who is responsible for ensuring this reliability?</t>
-        </is>
-      </c>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -2130,10 +2130,16 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Which specific languages must be supported to meet the threshold and goal?
+What aspects of the application must be localized (UI, help content, notifications, etc.)?
+How will language support be verified (e.g., user acceptance testing, automated checks)?</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -2207,9 +2213,10 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>What does 'adequate' mean in measurable terms (e.g., specific performance or quality criteria)?
-When will the 'Threshold (Accept)' value be finalized?
-Which actor or system is responsible for meeting this requirement?</t>
+          <t>Under what conditions is error logging required?
+What types of errors must be logged?
+What information should be included in each error log entry?
+How will compliance with error logging be verified?</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2280,13 +2287,14 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>What specific unit should be associated with the 'Threshold (Accept)' value?
-Under what specific conditions is this requirement considered 'required'?</t>
+          <t>What specific behaviors are expected during and after a network interruption (e.g., retry logic, user notifications, data preservation)?
+How long should the system attempt to recover from an interruption?
+How will robustness be measured or tested?</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -3359,9 +3367,9 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>What is the maximum acceptable response time in milliseconds?
-Which component — frontend, backend, or network — owns this response time requirement?
-Under what load conditions (e.g., concurrent users, requests per second) must this requirement be met?</t>
+          <t>What specific metric or range defines 'optimal' performance?
+Which system or component is responsible for achieving this performance?
+What are the measurable success criteria for this requirement?</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -3437,9 +3445,9 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>What unit should be applied to the Threshold (Accept) value?
-Who or what system is responsible for achieving this requirement?
-What is the ideal design target value in measurable terms?</t>
+          <t>What units should be used for the provided threshold?
+Who or what system is responsible for meeting this threshold?
+Are there any specific conditions under which this threshold should be tested?</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
@@ -3587,9 +3595,9 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>What specific criteria define 'appropriate' in this context?
-What is the minimum acceptable threshold (e.g., numeric or categorical value)?
-Who or what system is responsible for fulfilling this requirement?</t>
+          <t>Under what specific conditions would this requirement be applicable?
+What is the target value or range for the 'Goal (Design Target)'?
+Which system or team is responsible for implementing this requirement?</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -3665,9 +3673,9 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>What are the exact success criteria for this requirement?
-Who is responsible for implementing and validating this requirement?
-Are there any boundary conditions or edge cases that should be explicitly stated?</t>
+          <t>What measurable criteria define 'sufficient' in this context?
+Are there any benchmarks or thresholds that should be met?
+Which actor or system is responsible for ensuring sufficiency?</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
@@ -4761,1409 +4769,1411 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
+          <t>What specific metric or criteria defines 'efficient' in this context?
+What is the acceptable range or value for the Threshold (Accept)?
+Which system or actor is responsible for ensuring efficiency?</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>83</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Scan Setup Intuitiveness</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Improve intuitiveness of setup for 'Scan to Email' on the control panel, especially for macOS, by incorporating scan setup into the OOBE workflow.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Customers have challenges setting up scan to email. Currently, scan features require EWS or full driver. Incorporating scan setup into OOBE can provide a seamless experience.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Accept - Goal</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>What units should be applied to the Threshold (Accept)?
+What criteria determine whether the configuration is 'appropriate'?</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>84</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Setup Poster and SW Installation</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Provide a clear and concise setup poster with color and appropriate size, including clear instructions for software installation after hardware setup is complete.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Customers might not know software installation is required after hardware setup. The 'Thank you for using HP' screen misleads users to think the printer is ready. Clear guide on Print Zone Area and SW installation is needed.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>85</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>UI Tips and Tricks</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>['Manhattan']</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Display tips and tricks on the UI between print jobs to create awareness of printer features.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Useful tips are available in Help button; creating awareness on features and tips can enhance user experience.</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>What specific performance metrics define 'robust' in this context?
+What is the acceptable range or value for the Threshold (Accept)?
+What specific conditions or scenarios must the system handle to be considered robust?</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>86</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Crystal Chook</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Quiet Mode Awareness</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>['Manhattan']</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Make Quiet Mode ON/OFF option obvious and easily understood on the UI, especially during copying.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Most users are unaware of Quiet Mode availability during copying. Making it obvious improves user control and satisfaction.</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>What are the exact lower and upper bounds for the Threshold (Accept)?
+Which system or actor is responsible for meeting this requirement?</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>87</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Crystal Chook</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Accessibility - Color Contrast</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>['Marconi']</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Ensure all hardware controls and keys meet color contrast requirements: normal text and graphics 4.5:1 ratio, text &gt;= 18pt 3:1 ratio, and buttons must be either 'Light on Dark' or 'Dark on Light'.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Control Panel CGD meets minimum contrast requirements, ensuring accessibility compliance.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>88</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Crystal Chook</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Accessibility - Hardware Touch Points Identification</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>['Marconi', 'Manhattan', 'Moreto', 'Kebin']</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Ensure identification of hardware touch points does not rely solely on color for user perception (e.g., use CMYK alphabet marking for cartridges and labels in PHA slot).</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Color is not the sole means for user perception; additional markings improve accessibility and usability.</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>89</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Crystal Chook</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Electronic Document User Guide - Color Contrast</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Ensure all electronic document user guide content displays correctly in high contrast OS themes (Black and White, and color contrast). Normal text and graphics must have a 4.5:1 ratio; text &gt;= 18pt must have a 3:1 ratio.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>All content must display correctly in high contrast themes for accessibility, especially for Windows OS.</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>90</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Crystal Chook</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Electronic Document User Guide - Magnifier Compatibility</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Ensure all electronic document user guide content is compatible with Magnifier features.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Content must be compatible with Magnifier features for accessibility, especially for Windows OS.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>92</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Crystal Chook</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Electronic Document User Guide - Accessibility Section</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ensure the engine door affordance is clear: the arrow to open the engine door must be blue to help customers locate and open it for ink changes or paper jam access, especially when the door is closed.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Generic accessibility information and detailed product features that have accessibility conformance must be included.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>93</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Crystal Chook</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Tilt left and right each while printing</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>94</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Mandy Hagedorn</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>OOBE</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>OOBE</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>The methods are listed in order the user should see them: Power on, Connect to wireless or USB, Get HP Smart SW based on preferred method (PC, Mobile) and user should easily be able to identify and find</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>20210608 (Celine): Pending for MMA OOBE design flow; waiting resource
+20220301: Overall OOBE sta</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>95</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Mandy Hagedorn</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>OOBE</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>OOBE</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>During setup, to support paper/ink installation, an animated visual during OOBE to demonstrate how to install ink and paper is highly desired</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>20210608 (Celine): Pending for MMA OOBE design flow; waiting resource
+20220301: (Uday) Overall OOBE strategy in still in progress. By Solution IL we may have the clarity on different paths.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>100</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>celine Taccori</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>customer experience</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>customer experience</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Engine door affordance</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>102</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>celine Taccori</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>customer experience</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>customer experience</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Yellow (CISS, Manhattan Plus, XXL, Marconi)</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Engine door affordance</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Alden/Celine: we have a concept sent to TH Ang, and he is able to create in CD2. Althought investment dollar exceeded, quality and design still championing the idea and thinking about alternative to achieve intent.</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Accept - Goal</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>103</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Mandy Hagedorn</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Yellow (CISS, Manhattan Plus, XXL, Marconi)</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>All system status indicators must be discernible visually, by touch, or by sound, supporting accessibility.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Same as 3M</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Same as 3M</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>104</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Mandy Hagedorn</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Out-of-Box Experience (OOBE)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Yellow (CISS, Manhattan Plus, XXL, Marconi)</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Printed instructions must clearly list setup steps in order: Power on, connect to wireless or USB, obtain HP Smart software for PC or mobile, and ensure users can easily identify each step.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Same as 3M</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Same as 3M</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>105</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Out-of-Box Experience (OOBE)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Yellow (CISS, Manhattan Plus, XXL, Marconi)</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>During setup, provide an animated visual in the OOBE flow to demonstrate ink and paper installation.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Based on aligned proposal to Premal/Albert, pending approval for budget</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Threshold/Goal discussed &amp; updated</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>106</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Mandy Hagedorn</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Out-of-Box Experience (OOBE)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Grey (USB-only, Wi-Fi/Ethernet depending on SKU)</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Include a setup card in the box for each setup mode (wireless or USB for mobile or PC), tailored to the SKU's supported connectivity.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>same as 3M Yeti (software &amp; some reports does not see "e")</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>same as 3M Yeti</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>107</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Customer Experience</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Grey (Wi-Fi troubleshooting table in RG)</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Setup instructions should include a FAQ section and a diagram of the control panel; if not feasible, include a troubleshooting table covering common issues.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Better than current Manhattan units. Threshold is HP Smart scan capability as is in S'21</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>HP Smart scan capability as is in S'21</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>108</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Support Experience (Self HEAL)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Grey (HP+ flyer, SmartApp)</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Include HP+ specific instructions in relevant learning materials (print and digital) for applicable SKUs.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>same with predecessor HP Smart Diagnose</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>same with predecessor HP Smart Diagnose</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
           <t>What is the maximum acceptable response time in milliseconds?
 Which component — frontend, backend, or network — owns this response time requirement?
 Under what load conditions (concurrent users, requests/second) must this be met?</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>83</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Tracy Foo</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Scan Setup Intuitiveness</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Improve intuitiveness of setup for 'Scan to Email' on the control panel, especially for macOS, by incorporating scan setup into the OOBE workflow.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Customers have challenges setting up scan to email. Currently, scan features require EWS or full driver. Incorporating scan setup into OOBE can provide a seamless experience.</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Accept - Goal</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>84</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Tracy Foo</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Setup Poster and SW Installation</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Provide a clear and concise setup poster with color and appropriate size, including clear instructions for software installation after hardware setup is complete.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Customers might not know software installation is required after hardware setup. The 'Thank you for using HP' screen misleads users to think the printer is ready. Clear guide on Print Zone Area and SW installation is needed.</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>What are the conditions that determine when additional languages are 'needed'?
-Who is responsible for implementing language support?
-What is the minimum number of languages that must be supported for acceptance?
-How will support for 'all EU languages' be verified and tested?</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>85</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Tracy Foo</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>UI Tips and Tricks</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>['Manhattan']</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Display tips and tricks on the UI between print jobs to create awareness of printer features.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Useful tips are available in Help button; creating awareness on features and tips can enhance user experience.</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>WANT</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>WANT</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>86</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Crystal Chook</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Quiet Mode Awareness</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>['Manhattan']</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Make Quiet Mode ON/OFF option obvious and easily understood on the UI, especially during copying.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Most users are unaware of Quiet Mode availability during copying. Making it obvious improves user control and satisfaction.</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>WANT</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>WANT</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>How will 'intuitive' and 'user-friendly' be measured (e.g., usability score, user testing results)?
-Who is responsible for evaluating the user interface?
-What is the minimum acceptable user satisfaction score or metric?
-What is the testable pass/fail condition for UI acceptance?</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>87</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Crystal Chook</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Accessibility - Color Contrast</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>['Marconi']</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Ensure all hardware controls and keys meet color contrast requirements: normal text and graphics 4.5:1 ratio, text &gt;= 18pt 3:1 ratio, and buttons must be either 'Light on Dark' or 'Dark on Light'.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Control Panel CGD meets minimum contrast requirements, ensuring accessibility compliance.</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>88</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Crystal Chook</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Accessibility - Hardware Touch Points Identification</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>['Marconi', 'Manhattan', 'Moreto', 'Kebin']</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Ensure identification of hardware touch points does not rely solely on color for user perception (e.g., use CMYK alphabet marking for cartridges and labels in PHA slot).</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Color is not the sole means for user perception; additional markings improve accessibility and usability.</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>89</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Crystal Chook</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Electronic Document User Guide - Color Contrast</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Ensure all electronic document user guide content displays correctly in high contrast OS themes (Black and White, and color contrast). Normal text and graphics must have a 4.5:1 ratio; text &gt;= 18pt must have a 3:1 ratio.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>All content must display correctly in high contrast themes for accessibility, especially for Windows OS.</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>90</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Crystal Chook</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Electronic Document User Guide - Magnifier Compatibility</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Ensure all electronic document user guide content is compatible with Magnifier features.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Content must be compatible with Magnifier features for accessibility, especially for Windows OS.</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>92</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Crystal Chook</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Electronic Document User Guide - Accessibility Section</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Ensure the engine door affordance is clear: the arrow to open the engine door must be blue to help customers locate and open it for ink changes or paper jam access, especially when the door is closed.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Generic accessibility information and detailed product features that have accessibility conformance must be included.</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>93</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Crystal Chook</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Tilt left and right each while printing</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>94</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Mandy Hagedorn</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>OOBE</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>OOBE</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>The methods are listed in order the user should see them: Power on, Connect to wireless or USB, Get HP Smart SW based on preferred method (PC, Mobile) and user should easily be able to identify and find</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>20210608 (Celine): Pending for MMA OOBE design flow; waiting resource
-20220301: Overall OOBE sta</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>95</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Mandy Hagedorn</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>OOBE</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>OOBE</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>During setup, to support paper/ink installation, an animated visual during OOBE to demonstrate how to install ink and paper is highly desired</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>20210608 (Celine): Pending for MMA OOBE design flow; waiting resource
-20220301: (Uday) Overall OOBE strategy in still in progress. By Solution IL we may have the clarity on different paths.</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>100</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>celine Taccori</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>customer experience</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>customer experience</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Engine door affordance</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>102</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>celine Taccori</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>customer experience</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>customer experience</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Yellow (CISS, Manhattan Plus, XXL, Marconi)</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Engine door affordance</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Alden/Celine: we have a concept sent to TH Ang, and he is able to create in CD2. Althought investment dollar exceeded, quality and design still championing the idea and thinking about alternative to achieve intent.</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Accept - Goal</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>103</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Mandy Hagedorn</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Experience</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Yellow (CISS, Manhattan Plus, XXL, Marconi)</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>All system status indicators must be discernible visually, by touch, or by sound, supporting accessibility.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Same as 3M</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Same as 3M</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>104</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Mandy Hagedorn</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Experience</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Out-of-Box Experience (OOBE)</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Yellow (CISS, Manhattan Plus, XXL, Marconi)</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Printed instructions must clearly list setup steps in order: Power on, connect to wireless or USB, obtain HP Smart software for PC or mobile, and ensure users can easily identify each step.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Same as 3M</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Same as 3M</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>105</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Itsushi Wakabayashi</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Experience</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Out-of-Box Experience (OOBE)</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Yellow (CISS, Manhattan Plus, XXL, Marconi)</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>During setup, provide an animated visual in the OOBE flow to demonstrate ink and paper installation.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Based on aligned proposal to Premal/Albert, pending approval for budget</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Threshold/Goal discussed &amp; updated</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>106</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Mandy Hagedorn</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Experience</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Out-of-Box Experience (OOBE)</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Grey (USB-only, Wi-Fi/Ethernet depending on SKU)</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Include a setup card in the box for each setup mode (wireless or USB for mobile or PC), tailored to the SKU's supported connectivity.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>same as 3M Yeti (software &amp; some reports does not see "e")</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>same as 3M Yeti</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>107</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Tracy Foo</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Customer Experience</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Grey (Wi-Fi troubleshooting table in RG)</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Setup instructions should include a FAQ section and a diagram of the control panel; if not feasible, include a troubleshooting table covering common issues.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Better than current Manhattan units. Threshold is HP Smart scan capability as is in S'21</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>HP Smart scan capability as is in S'21</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>WANT</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>108</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Tracy Foo</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Support Experience (Self HEAL)</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Grey (HP+ flyer, SmartApp)</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Include HP+ specific instructions in relevant learning materials (print and digital) for applicable SKUs.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>same with predecessor HP Smart Diagnose</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>same with predecessor HP Smart Diagnose</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>WANT</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>What is the maximum acceptable response time in milliseconds?
-Which component — frontend, backend, or network — owns this response time requirement?
-Under what load conditions (concurrent users, requests/second) must this be met?</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
@@ -7524,9 +7534,9 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>What is the maximum acceptable response time in milliseconds?
-Which component — frontend, backend, or network — owns this response time requirement?
-Under what load conditions (concurrent users, requests/second) must this be met?</t>
+          <t>What specific performance metric defines 'efficient' (e.g., latency, throughput)?
+What is the minimum acceptable threshold for this metric, including units?
+Which system or actor is responsible for ensuring this efficiency?</t>
         </is>
       </c>
       <c r="P102" t="inlineStr"/>
@@ -7597,10 +7607,16 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr"/>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>What specific numeric value or range constitutes 'adequate capacity'?
+What units should be used to measure this capacity (e.g., GB, users, transactions/second)?
+Which component is responsible for maintaining this capacity?</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr"/>
     </row>
     <row r="104">
@@ -7669,14 +7685,12 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>What specific authentication mechanisms or protocols are required (e.g., OAuth2, multi-factor authentication)?
-What are the measurable criteria for 'robust' authentication (e.g., resistance to brute-force attacks, minimum password complexity)?
-Who is responsible for implementing and maintaining user authentication?</t>
-        </is>
-      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
@@ -7743,12 +7757,16 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Which specific languages must the application support at minimum?
-What is the ideal set of languages to be supported?
-What does 'support' entail (e.g., full UI translation, help documentation, error messages)?</t>
+          <t>What specific failure scenarios or conditions define 'robust'?
+What are the minimum acceptable thresholds for robustness (e.g., uptime percentage, error rate)?
+Which actor or system is responsible for ensuring robustness?</t>
         </is>
       </c>
       <c r="P105" t="inlineStr"/>
@@ -7817,12 +7835,15 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>What is the minimum acceptable system uptime percentage (e.g., 99.9%)?
-What is the ideal system uptime target?
-Over what time period is uptime measured (e.g., monthly, annually)?</t>
+          <t>What is the exact numeric threshold for this requirement, including units?
+Under what specific conditions (e.g., load, environment) must this threshold be met?</t>
         </is>
       </c>
       <c r="P106" t="inlineStr"/>

--- a/output/prd_hitl.xlsx
+++ b/output/prd_hitl.xlsx
@@ -569,9 +569,9 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>What specific metric defines 'efficient' in this context (e.g., CPU usage, memory consumption)?
-What is the acceptable range or threshold for this efficiency metric?
-Who or what system component is responsible for ensuring efficiency?</t>
+          <t>What is the maximum acceptable response time in milliseconds?
+Which component — frontend, backend, or network — owns this response time requirement?
+Under what load conditions (concurrent users, requests/second) must this be met?</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -646,16 +646,10 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>What specific metric defines 'sufficient capacity' (e.g., GB, number of users)?
-What is the unit of measurement for the provided threshold?
-Which system component is responsible for meeting this capacity requirement?</t>
-        </is>
-      </c>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>The system shall provide secure paper-clearance procedures that prevent unauthorized access, damage, or safety hazards during maintenance.</t>
@@ -726,12 +720,16 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>What is the minimum number of concurrent users the application must support (threshold)?
+What is the ideal (design target) number of concurrent users?
+How is 'concurrent user' defined (active sessions, logged-in users, requests per second)?
+How will the system's ability to handle concurrent users be tested?
+Are there specific performance metrics (e.g., response time, error rate) under load?</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Minimum required improvement shall be defined as a measurable increase over the current baseline performance (e.g., ≥10% improvement unless otherwise specified).</t>
@@ -802,16 +800,14 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>What specific attributes or metrics define 'robust' in this context (e.g., uptime percentage, error tolerance)?
-What is the acceptable threshold or range for these robustness metrics?
-Which system or component is responsible for ensuring robustness?</t>
+          <t>What usability metrics or standards should be used to define 'intuitive' and 'easy to use' (e.g., SUS score, task completion rate)?
+Is there a target user group or persona for usability testing?
+What is the minimum acceptable usability score or user satisfaction rating?
+How will usability be measured and validated?
+Are there specific accessibility or design guidelines to follow?</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -884,16 +880,14 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>What specific conditions determine when this requirement is 'needed'?
-What system or actor is responsible for executing this requirement when needed?
-Is there a default behavior if the condition is not met?</t>
+          <t>What is the minimum acceptable system uptime percentage (e.g., 99.9%)?
+What is the ideal (design target) uptime?
+Over what period is uptime measured (monthly, yearly)?
+Does uptime include scheduled maintenance windows?
+How will uptime be monitored and reported?</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -3367,9 +3361,9 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>What specific metric or range defines 'optimal' performance?
-Which system or component is responsible for achieving this performance?
-What are the measurable success criteria for this requirement?</t>
+          <t>What is the maximum acceptable response time in milliseconds?
+Which component — frontend, backend, or network — owns this response time requirement?
+Under what load conditions (concurrent users, requests/second) must this be met?</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -3440,16 +3434,10 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>What units should be used for the provided threshold?
-Who or what system is responsible for meeting this threshold?
-Are there any specific conditions under which this threshold should be tested?</t>
-        </is>
-      </c>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -3516,12 +3504,15 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Which specific languages must be supported at minimum?
+What is the ideal set of languages to support?
+Does 'support' mean full UI translation, content translation, or both?
+Are there any compliance or localization standards to follow?</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -3588,16 +3579,13 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Under what specific conditions would this requirement be applicable?
-What is the target value or range for the 'Goal (Design Target)'?
-Which system or team is responsible for implementing this requirement?</t>
+          <t>Under what conditions must the system log errors?
+What types of errors must be logged?
+What information should be included in each error log?
+What is the minimum acceptable logging frequency or retention policy?</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -3666,16 +3654,13 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>What measurable criteria define 'sufficient' in this context?
-Are there any benchmarks or thresholds that should be met?
-Which actor or system is responsible for ensuring sufficiency?</t>
+          <t>What usability standards or metrics define 'user-friendly' (e.g., SUS score, error rate, task completion time)?
+Are there specific user personas or accessibility requirements to consider?
+What is the minimum acceptable usability score or benchmark?
+How will user-friendliness be tested and validated?</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
@@ -4769,9 +4754,9 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>What specific metric or criteria defines 'efficient' in this context?
-What is the acceptable range or value for the Threshold (Accept)?
-Which system or actor is responsible for ensuring efficiency?</t>
+          <t>What is the maximum acceptable response time in milliseconds?
+Which component — frontend, backend, or network — owns this response time requirement?
+Under what load conditions (concurrent users, requests/second) must this be met?</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
@@ -4842,15 +4827,10 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>What units should be applied to the Threshold (Accept)?
-What criteria determine whether the configuration is 'appropriate'?</t>
-        </is>
-      </c>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -4919,10 +4899,17 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr"/>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>What are the conditions that determine when additional languages are 'needed'?
+Who is responsible for implementing language support?
+What is the minimum number of languages that must be supported for acceptance?
+How will support for 'all EU languages' be verified and tested?</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -4991,16 +4978,10 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>What specific performance metrics define 'robust' in this context?
-What is the acceptable range or value for the Threshold (Accept)?
-What specific conditions or scenarios must the system handle to be considered robust?</t>
-        </is>
-      </c>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
@@ -5069,13 +5050,15 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>What are the exact lower and upper bounds for the Threshold (Accept)?
-Which system or actor is responsible for meeting this requirement?</t>
+          <t>How will 'intuitive' and 'user-friendly' be measured (e.g., usability score, user testing results)?
+Who is responsible for evaluating the user interface?
+What is the minimum acceptable user satisfaction score or metric?
+What is the testable pass/fail condition for UI acceptance?</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
@@ -6242,10 +6225,15 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr"/>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>What units should be used for the 'Goal (Design Target)' value?
+Who is responsible for achieving this requirement — the system or a specific subsystem?</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
@@ -6308,14 +6296,12 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>Which specific languages must the application support at minimum?
-What is the target number or list of languages for full support?
-What does 'support' entail (UI translation, content localization, input validation, etc.)?</t>
-        </is>
-      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
@@ -6378,12 +6364,16 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Under what specific conditions should notifications be sent to users?
-Who or what determines when a notification is necessary?
-What is the acceptable delivery time for notifications (e.g., within X seconds of event)?</t>
+          <t>What specific metric defines 'adequate' in this context?
+What are the minimum acceptable values or thresholds for this requirement?
+Which system component is responsible for meeting this requirement?</t>
         </is>
       </c>
       <c r="P85" t="inlineStr"/>
@@ -6448,12 +6438,15 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>What is the minimum acceptable system uptime percentage (e.g., 99.9%)?
-What is the target system uptime percentage?
-Over what time period is uptime measured (monthly, yearly)?</t>
+          <t>Can you clarify the units for the 'Threshold (Accept)' value?
+Who or what system is responsible for meeting this requirement?</t>
         </is>
       </c>
       <c r="P86" t="inlineStr"/>
@@ -7534,9 +7527,9 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>What specific performance metric defines 'efficient' (e.g., latency, throughput)?
-What is the minimum acceptable threshold for this metric, including units?
-Which system or actor is responsible for ensuring this efficiency?</t>
+          <t>What specific metric or criteria defines 'efficient' in this context?
+Who or what system is responsible for achieving this efficiency?
+What is the minimum acceptable threshold for this requirement, and what units should be used?</t>
         </is>
       </c>
       <c r="P102" t="inlineStr"/>
@@ -7612,9 +7605,9 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>What specific numeric value or range constitutes 'adequate capacity'?
-What units should be used to measure this capacity (e.g., GB, users, transactions/second)?
-Which component is responsible for maintaining this capacity?</t>
+          <t>What specific power level (in watts or another unit) is considered 'adequate'?
+Which component or actor is responsible for ensuring this power level?
+Are there any environmental or operational conditions under which this requirement must be met?</t>
         </is>
       </c>
       <c r="P103" t="inlineStr"/>
@@ -7764,9 +7757,9 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>What specific failure scenarios or conditions define 'robust'?
-What are the minimum acceptable thresholds for robustness (e.g., uptime percentage, error rate)?
-Which actor or system is responsible for ensuring robustness?</t>
+          <t>What specific reliability metric (e.g., uptime percentage, mean time between failures) is expected?
+Who or what system is responsible for ensuring reliability?
+What is the minimum acceptable threshold for reliability, and what is the design target?</t>
         </is>
       </c>
       <c r="P105" t="inlineStr"/>
@@ -7842,8 +7835,9 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>What is the exact numeric threshold for this requirement, including units?
-Under what specific conditions (e.g., load, environment) must this threshold be met?</t>
+          <t>What are the exact upper and lower bounds for the specified range?
+Which component or actor is responsible for meeting this range?
+Under what specific conditions or scenarios must this range be maintained?</t>
         </is>
       </c>
       <c r="P106" t="inlineStr"/>
